--- a/HRM_mini_vn_2025-2026.xlsx
+++ b/HRM_mini_vn_2025-2026.xlsx
@@ -473,7 +473,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G312"/>
+  <dimension ref="A1:G323"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7651,9 +7651,262 @@
         <v>Thêm chấm công ngày 2026-06-16 của Phạm Gia Trí</v>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>LOG-000312</v>
+      </c>
+      <c r="B313" t="str">
+        <v>2026-06-16 14:32:10</v>
+      </c>
+      <c r="C313" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D313" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E313" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F313" t="str">
+        <v>ATT-000809</v>
+      </c>
+      <c r="G313" t="str">
+        <v>Thêm chấm công ngày 2026-06-16 của Trần Tuấn An</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>LOG-000313</v>
+      </c>
+      <c r="B314" t="str">
+        <v>2026-06-16 14:32:33</v>
+      </c>
+      <c r="C314" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D314" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E314" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F314" t="str">
+        <v>ATT-000810</v>
+      </c>
+      <c r="G314" t="str">
+        <v>Thêm chấm công ngày 2026-06-03 của Phạm Gia Trí</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>LOG-000314</v>
+      </c>
+      <c r="B315" t="str">
+        <v>2026-06-16 14:32:41</v>
+      </c>
+      <c r="C315" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D315" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E315" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F315" t="str">
+        <v>ATT-000811</v>
+      </c>
+      <c r="G315" t="str">
+        <v>Thêm chấm công ngày 2026-06-12 của Phạm Gia Trí</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>LOG-000315</v>
+      </c>
+      <c r="B316" t="str">
+        <v>2026-06-16 14:32:48</v>
+      </c>
+      <c r="C316" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D316" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E316" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F316" t="str">
+        <v>ATT-000812</v>
+      </c>
+      <c r="G316" t="str">
+        <v>Thêm chấm công ngày 2026-06-16 của Phạm Gia Trí</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>LOG-000316</v>
+      </c>
+      <c r="B317" t="str">
+        <v>2026-06-18 12:36:28</v>
+      </c>
+      <c r="C317" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D317" t="str">
+        <v>DELETE</v>
+      </c>
+      <c r="E317" t="str">
+        <v>phong-ban</v>
+      </c>
+      <c r="F317" t="str">
+        <v>DEP-0005</v>
+      </c>
+      <c r="G317" t="str">
+        <v>Xóa phòng ban: Tài chính - Kế toán</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>LOG-000317</v>
+      </c>
+      <c r="B318" t="str">
+        <v>2026-06-18 12:41:36</v>
+      </c>
+      <c r="C318" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D318" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E318" t="str">
+        <v>don-xin-nghi</v>
+      </c>
+      <c r="F318" t="str">
+        <v>LV-000009</v>
+      </c>
+      <c r="G318" t="str">
+        <v>Tạo đơn Nghỉ phép năm của Huỳnh Minh Trang (1 ngày)</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>LOG-000318</v>
+      </c>
+      <c r="B319" t="str">
+        <v>2026-06-18 12:46:02</v>
+      </c>
+      <c r="C319" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D319" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E319" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F319" t="str">
+        <v>ATT-000813</v>
+      </c>
+      <c r="G319" t="str">
+        <v>Thêm chấm công ngày 2026-06-18 của Phạm Gia Trí</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>LOG-000319</v>
+      </c>
+      <c r="B320" t="str">
+        <v>2026-06-23 10:33:49</v>
+      </c>
+      <c r="C320" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D320" t="str">
+        <v>CREATE</v>
+      </c>
+      <c r="E320" t="str">
+        <v>nhan-vien</v>
+      </c>
+      <c r="F320" t="str">
+        <v>EMP-000049</v>
+      </c>
+      <c r="G320" t="str">
+        <v>Thêm mới nhân viên NAM test (NV-0049)</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>LOG-000320</v>
+      </c>
+      <c r="B321" t="str">
+        <v>2026-06-23 10:34:41</v>
+      </c>
+      <c r="C321" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D321" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="E321" t="str">
+        <v>nhan-vien</v>
+      </c>
+      <c r="F321" t="str">
+        <v>EMP-000049</v>
+      </c>
+      <c r="G321" t="str">
+        <v>Cập nhật nhân viên NAM test (NV-0049)</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>LOG-000321</v>
+      </c>
+      <c r="B322" t="str">
+        <v>2026-06-23 10:51:04</v>
+      </c>
+      <c r="C322" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D322" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="E322" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F322" t="str">
+        <v>ATT-000809</v>
+      </c>
+      <c r="G322" t="str">
+        <v>Cập nhật chấm công ngày 2026-06-23 của Trần Tuấn An</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>LOG-000322</v>
+      </c>
+      <c r="B323" t="str">
+        <v>2026-06-23 10:51:16</v>
+      </c>
+      <c r="C323" t="str">
+        <v>admin</v>
+      </c>
+      <c r="D323" t="str">
+        <v>UPDATE</v>
+      </c>
+      <c r="E323" t="str">
+        <v>cham-cong</v>
+      </c>
+      <c r="F323" t="str">
+        <v>ATT-000813</v>
+      </c>
+      <c r="G323" t="str">
+        <v>Cập nhật chấm công ngày 2026-06-23 của Phạm Gia Trí</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G312"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G323"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7932,7 +8185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8036,16 +8289,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>DEP-0005</v>
+        <v>DEP-0006</v>
       </c>
       <c r="B6" t="str">
-        <v>Tài chính - Kế toán</v>
+        <v>Nhân sự</v>
       </c>
       <c r="C6" t="str">
-        <v>CC-FIN</v>
+        <v>CC-HR</v>
       </c>
       <c r="D6" t="str">
-        <v>EMP-000005</v>
+        <v>EMP-000006</v>
       </c>
       <c r="E6" t="str">
         <v>active</v>
@@ -8054,30 +8307,9 @@
         <v>2024-01-01</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>DEP-0006</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Nhân sự</v>
-      </c>
-      <c r="C7" t="str">
-        <v>CC-HR</v>
-      </c>
-      <c r="D7" t="str">
-        <v>EMP-000006</v>
-      </c>
-      <c r="E7" t="str">
-        <v>active</v>
-      </c>
-      <c r="F7" t="str">
-        <v>2024-01-01</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -8216,7 +8448,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10618,10 +10850,59 @@
         <v>2024-01-01</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>EMP-000049</v>
+      </c>
+      <c r="B49" t="str">
+        <v>NV-0049</v>
+      </c>
+      <c r="C49" t="str">
+        <v>NAM test</v>
+      </c>
+      <c r="D49" t="str">
+        <v>male</v>
+      </c>
+      <c r="E49" t="str">
+        <v>1995-01-01</v>
+      </c>
+      <c r="F49" t="str">
+        <v>123123</v>
+      </c>
+      <c r="G49" t="str">
+        <v>phamv0961@gmail.com</v>
+      </c>
+      <c r="H49" t="str">
+        <v>HN</v>
+      </c>
+      <c r="I49" t="str">
+        <v>DEP-0001</v>
+      </c>
+      <c r="J49" t="str">
+        <v>POS-0004</v>
+      </c>
+      <c r="K49" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="L49" t="str">
+        <v>official</v>
+      </c>
+      <c r="M49">
+        <v>15000000</v>
+      </c>
+      <c r="N49" t="str">
+        <v>123</v>
+      </c>
+      <c r="O49" t="str">
+        <v>active</v>
+      </c>
+      <c r="P49" t="str">
+        <v>2026-06-23</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P49"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -10755,7 +11036,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11717,16 +11998,176 @@
         <v/>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>ATT-000809</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="C31" t="str">
+        <v>EMP-000018</v>
+      </c>
+      <c r="D31" t="str">
+        <v>SHF-0001</v>
+      </c>
+      <c r="E31" t="str">
+        <v>2026-06-23 08:00:00</v>
+      </c>
+      <c r="F31" t="str">
+        <v>2026-06-23 13:33:00</v>
+      </c>
+      <c r="G31">
+        <v>8</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31" t="str">
+        <v>early-leave</v>
+      </c>
+      <c r="J31" t="str">
+        <v>bận</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>ATT-000810</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C32" t="str">
+        <v>EMP-000001</v>
+      </c>
+      <c r="D32" t="str">
+        <v>SHF-0001</v>
+      </c>
+      <c r="E32" t="str">
+        <v>2026-06-03 08:00:00</v>
+      </c>
+      <c r="F32" t="str">
+        <v>2026-06-03 19:30:00</v>
+      </c>
+      <c r="G32">
+        <v>8</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32" t="str">
+        <v>overtime</v>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>ATT-000811</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2026-06-12</v>
+      </c>
+      <c r="C33" t="str">
+        <v>EMP-000001</v>
+      </c>
+      <c r="D33" t="str">
+        <v>SHF-0001</v>
+      </c>
+      <c r="E33" t="str">
+        <v>2026-06-12 08:00:00</v>
+      </c>
+      <c r="F33" t="str">
+        <v>2026-06-12 17:30:00</v>
+      </c>
+      <c r="G33">
+        <v>8</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33" t="str">
+        <v>present</v>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>ATT-000812</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2026-06-16</v>
+      </c>
+      <c r="C34" t="str">
+        <v>EMP-000001</v>
+      </c>
+      <c r="D34" t="str">
+        <v>SHF-0001</v>
+      </c>
+      <c r="E34" t="str">
+        <v>2026-06-16 08:00:00</v>
+      </c>
+      <c r="F34" t="str">
+        <v>2026-06-16 17:30:00</v>
+      </c>
+      <c r="G34">
+        <v>8</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34" t="str">
+        <v>absent</v>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>ATT-000813</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2026-06-23</v>
+      </c>
+      <c r="C35" t="str">
+        <v>EMP-000001</v>
+      </c>
+      <c r="D35" t="str">
+        <v>SHF-0001</v>
+      </c>
+      <c r="E35" t="str">
+        <v>2026-06-23 09:00:00</v>
+      </c>
+      <c r="F35" t="str">
+        <v>2026-06-23 16:30:00</v>
+      </c>
+      <c r="G35">
+        <v>8</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35" t="str">
+        <v>late</v>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J35"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11888,9 +12329,41 @@
         <v>2026-06-16T10:51:17.978Z</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LV-000009</v>
+      </c>
+      <c r="B6" t="str">
+        <v>EMP-000044</v>
+      </c>
+      <c r="C6" t="str">
+        <v>annual</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="E6" t="str">
+        <v>2026-06-18</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="str">
+        <v>làm đồ án</v>
+      </c>
+      <c r="H6" t="str">
+        <v>pending</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>2026-06-18T12:41:36.799Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>
